--- a/testakten/rentenrecht-erwerbsminderung-long-covid-pots-koeln/versicherungsverlauf_luecken_2026.xlsx
+++ b/testakten/rentenrecht-erwerbsminderung-long-covid-pots-koeln/versicherungsverlauf_luecken_2026.xlsx
@@ -7,9 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daten" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zeiten" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medizin" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Zeiten'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Zeiten'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Medizin'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Medizin'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +31,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00183941"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7EFF1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +63,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00C7D2D5"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -411,106 +443,541 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Zeitraum</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Beginn</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ende</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tatbestand</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Meldung DRV</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Nachweis</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Klärungsbedarf</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>zuständig</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2006-09-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2017-02-28</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Pflichtbeiträge Klinikum</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>gespeichert</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitgebermeldung</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>keiner</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>DRV</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2017-03-01</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2017-06-30</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Mutterschutz</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>gespeichert</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Kassenmeldung</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Monate abgleichen</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Frings</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2017-07-01</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2020-06-30</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Kindererziehungszeit</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>teilweise</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Geburtsurkunde Nele</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Zuordnung März 2018 fehlt</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>DRV</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2018-03-01</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Beschäftigung Klinikum</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>gespeichert</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Lohnkonto</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Überlappung Kinderzeit prüfen</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Frings</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Entgeltfortzahlung</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>gespeichert</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Abrechnung</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>keiner</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Klinikum</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Krankengeld</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>bis Februar gespeichert</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Kassenbescheinigung</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Märzmeldung fehlt</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Krankenkasse</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>medizinische Rehabilitation</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>gemeldet</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Entlassungsbericht</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Übergangsgeldbescheid fehlt</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>DRV</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>laufend</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Krankengeld</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Kontoauszüge</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Leistungsbescheinigung anfordern</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Krankenkasse</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unterlage</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Aussage</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Original vorhanden</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Offener Punkt</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2006-2012</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Pflichtbeiträge Pflege</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Lohnabrechnungen</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>vollständig</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Reha-Entlassungsbericht</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>drei bis unter sechs Stunden mit engen Bedingungen</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>vollständige Therapieanwesenheit anfordern</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2017-2018</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Kindererziehung</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Geburtsurkunde</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Zuordnung prüfen</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Kipptischprotokoll</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Herzfrequenzanstieg und Präsynkope</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Medikationspause dokumentiert</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2024-2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Krankengeld</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Kasse</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Bescheinigung März 2026 fehlt</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitgeberbescheinigung</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Versuch organisatorisch gescheitert</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Zeiterfassung beifügen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>DRV-Untersuchung</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>noch nicht in Akte</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Akteneinsicht</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Alltagsprotokoll</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Schwankung und Folgetage</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Pulsbilder sichern</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToWidth="1"/>
 </worksheet>
 </file>